--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -1967,7 +1967,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131154316</v>
+        <v>131154322</v>
       </c>
       <c r="B12" t="n">
         <v>79244</v>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445069</v>
+        <v>445001</v>
       </c>
       <c r="R12" t="n">
-        <v>7053221</v>
+        <v>7053337</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Växer på en tydligt gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2098,7 +2098,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131154322</v>
+        <v>131154316</v>
       </c>
       <c r="B13" t="n">
         <v>79244</v>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445001</v>
+        <v>445069</v>
       </c>
       <c r="R13" t="n">
-        <v>7053337</v>
+        <v>7053221</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växer på en tydligt gammal gran med grov bark.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>131154317</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>131154319</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131154323</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131154313</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>131154315</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131154324</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131154314</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131154322</v>
+        <v>131154316</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445001</v>
+        <v>445069</v>
       </c>
       <c r="R12" t="n">
-        <v>7053337</v>
+        <v>7053221</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Växer på en tydligt gammal gran med grov bark.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2098,10 +2098,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131154316</v>
+        <v>131154322</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445069</v>
+        <v>445001</v>
       </c>
       <c r="R13" t="n">
-        <v>7053221</v>
+        <v>7053337</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Växer på en tydligt gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2232,7 +2232,7 @@
         <v>131154318</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>131154321</v>
       </c>
       <c r="B15" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131154320</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131187652</v>
       </c>
       <c r="B17" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>131187651</v>
       </c>
       <c r="B22" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>131187650</v>
       </c>
       <c r="B23" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -2615,7 +2615,7 @@
         <v>131187652</v>
       </c>
       <c r="B17" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>131187651</v>
       </c>
       <c r="B22" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>131187650</v>
       </c>
       <c r="B23" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>131154317</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>131154319</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131154323</v>
+        <v>131154313</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445033</v>
+        <v>445053</v>
       </c>
       <c r="R6" t="n">
-        <v>7053229</v>
+        <v>7053130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,6 +1288,11 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1313,9 +1318,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1333,10 +1343,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131154313</v>
+        <v>131154323</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,10 +1381,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445053</v>
+        <v>445033</v>
       </c>
       <c r="R7" t="n">
-        <v>7053130</v>
+        <v>7053229</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,11 +1419,6 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1439,14 +1444,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
         <v>131154315</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131154324</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131154314</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>131154316</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131154322</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131154318</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>131154321</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131154320</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131187652</v>
       </c>
       <c r="B17" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>131187651</v>
       </c>
       <c r="B22" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>131187650</v>
       </c>
       <c r="B23" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154302</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154317</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>131154319</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131154303</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131154313</v>
+        <v>131154323</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445053</v>
+        <v>445033</v>
       </c>
       <c r="R6" t="n">
-        <v>7053130</v>
+        <v>7053229</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,11 +1288,6 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1318,14 +1313,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1343,10 +1333,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131154323</v>
+        <v>131154313</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,10 +1371,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445033</v>
+        <v>445053</v>
       </c>
       <c r="R7" t="n">
-        <v>7053229</v>
+        <v>7053130</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,6 +1409,11 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1444,9 +1439,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
         <v>131154315</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131154305</v>
       </c>
       <c r="B9" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131154324</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131154314</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>131154316</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131154322</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131154318</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>131154321</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131154320</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131187652</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>131187648</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>131187645</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>131187643</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>131187644</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>131187651</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>131187650</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154302</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154317</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>131154319</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131154303</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131154323</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131154313</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>131154315</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131154305</v>
       </c>
       <c r="B9" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131154324</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154314</v>
+        <v>131154316</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>445069</v>
       </c>
       <c r="R11" t="n">
-        <v>7053165</v>
+        <v>7053221</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131154316</v>
+        <v>131154322</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445069</v>
+        <v>445001</v>
       </c>
       <c r="R12" t="n">
-        <v>7053221</v>
+        <v>7053337</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Växer på en tydligt gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2098,10 +2098,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131154322</v>
+        <v>131154314</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445001</v>
+        <v>445069</v>
       </c>
       <c r="R13" t="n">
-        <v>7053337</v>
+        <v>7053165</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växer på en tydligt gammal gran med grov bark.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2232,7 +2232,7 @@
         <v>131154318</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>131154321</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131154320</v>
       </c>
       <c r="B16" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131187652</v>
       </c>
       <c r="B17" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>131187648</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>131187645</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>131187643</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>131187644</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>131187651</v>
       </c>
       <c r="B22" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>131187650</v>
       </c>
       <c r="B23" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -1836,7 +1836,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154316</v>
+        <v>131154314</v>
       </c>
       <c r="B11" t="n">
         <v>79249</v>
@@ -1877,7 +1877,7 @@
         <v>445069</v>
       </c>
       <c r="R11" t="n">
-        <v>7053221</v>
+        <v>7053165</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131154322</v>
+        <v>131154316</v>
       </c>
       <c r="B12" t="n">
         <v>79249</v>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445001</v>
+        <v>445069</v>
       </c>
       <c r="R12" t="n">
-        <v>7053337</v>
+        <v>7053221</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Växer på en tydligt gammal gran med grov bark.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2098,7 +2098,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131154314</v>
+        <v>131154322</v>
       </c>
       <c r="B13" t="n">
         <v>79249</v>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445069</v>
+        <v>445001</v>
       </c>
       <c r="R13" t="n">
-        <v>7053165</v>
+        <v>7053337</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Växer på en tydligt gammal gran med grov bark.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154302</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154317</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>131154319</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131154303</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131154323</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131154313</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>131154315</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131154324</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131154314</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>131154316</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131154322</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131154318</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>131154321</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131154320</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131187652</v>
       </c>
       <c r="B17" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>131187648</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>131187645</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>131187643</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>131187644</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>131187651</v>
       </c>
       <c r="B22" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>131187650</v>
       </c>
       <c r="B23" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154302</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154317</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>131154319</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131154303</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131154323</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131154313</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>131154315</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131154305</v>
       </c>
       <c r="B9" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131154324</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131154314</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>131154316</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131154322</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131154318</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>131154321</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131154320</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131187652</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>131187648</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>131187645</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>131187643</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>131187644</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>131187651</v>
       </c>
       <c r="B22" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>131187650</v>
       </c>
       <c r="B23" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154302</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154317</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>131154319</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131154303</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131154323</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131154313</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>131154315</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131154305</v>
       </c>
       <c r="B9" t="n">
-        <v>57070</v>
+        <v>57071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131154324</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131154314</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>131154316</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131154322</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131154318</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>131154321</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131154320</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131187652</v>
       </c>
       <c r="B17" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>131187648</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>131187645</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>131187643</v>
       </c>
       <c r="B20" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>131187644</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>131187651</v>
       </c>
       <c r="B22" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>131187650</v>
       </c>
       <c r="B23" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154302</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154317</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>131154319</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131154303</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131154323</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131154313</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>131154315</v>
       </c>
       <c r="B8" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131154305</v>
       </c>
       <c r="B9" t="n">
-        <v>57071</v>
+        <v>57077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>131154324</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131154314</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>131154316</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>131154322</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>131154318</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>131154321</v>
       </c>
       <c r="B15" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131154320</v>
       </c>
       <c r="B16" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131187652</v>
       </c>
       <c r="B17" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>131187648</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>131187645</v>
       </c>
       <c r="B19" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>131187643</v>
       </c>
       <c r="B20" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>131187644</v>
       </c>
       <c r="B21" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>131187651</v>
       </c>
       <c r="B22" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>131187650</v>
       </c>
       <c r="B23" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131154302</v>
+        <v>131154318</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444997</v>
+        <v>444968</v>
       </c>
       <c r="R2" t="n">
-        <v>7053491</v>
+        <v>7053470</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +751,13 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs några meter på en gran. Minst medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,12 +778,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,14 +801,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131154317</v>
+        <v>131154319</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -848,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445064</v>
+        <v>444990</v>
       </c>
       <c r="R3" t="n">
-        <v>7053303</v>
+        <v>7053496</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -941,14 +932,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131154319</v>
+        <v>131154320</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -979,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444990</v>
+        <v>444986</v>
       </c>
       <c r="R4" t="n">
-        <v>7053496</v>
+        <v>7053440</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Växer på en tydligt gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1072,42 +1063,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131154303</v>
+        <v>131154321</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1115,10 +1101,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444998</v>
+        <v>444974</v>
       </c>
       <c r="R5" t="n">
-        <v>7053477</v>
+        <v>7053372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,17 +1139,13 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), äldre, enstaka på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1172,11 +1154,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gammal granskog med frekvent förekomst av naturvärdesgranar med grov bark och hög ålder. Ställvis flerskiktat och luckigt.</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1189,12 +1166,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1212,14 +1189,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131154323</v>
+        <v>131154322</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1250,10 +1227,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445033</v>
+        <v>445001</v>
       </c>
       <c r="R6" t="n">
-        <v>7053229</v>
+        <v>7053337</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,6 +1265,11 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer på en tydligt gammal gran med grov bark.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1313,9 +1295,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1333,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131154313</v>
+        <v>131154302</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,26 +1331,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1371,10 +1363,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445053</v>
+        <v>444997</v>
       </c>
       <c r="R7" t="n">
-        <v>7053130</v>
+        <v>7053491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1403,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska och äldre, längs några meter på en gran. Minst medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,7 +1412,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1441,12 +1432,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1464,10 +1455,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131154315</v>
+        <v>131154303</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,26 +1466,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1502,10 +1498,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445094</v>
+        <v>444998</v>
       </c>
       <c r="R8" t="n">
-        <v>7053203</v>
+        <v>7053477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,13 +1536,17 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, enstaka på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1555,6 +1555,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal granskog med frekvent förekomst av naturvärdesgranar med grov bark och hög ålder. Ställvis flerskiktat och luckigt.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1565,9 +1570,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1585,10 +1595,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131154305</v>
+        <v>131187642</v>
       </c>
       <c r="B9" t="n">
-        <v>57077</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,16 +1606,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1618,20 +1628,20 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Bod-tjärnen Sydväst, Jmt</t>
+          <t>Nästflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444982</v>
+        <v>444975</v>
       </c>
       <c r="R9" t="n">
-        <v>7053382</v>
+        <v>7053521</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1668,47 +1678,37 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket och en nyligen använd lega inunder snön.</t>
+          <t>Troligt bohål av tretå ca 2,8m upp i en asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Flerskiktad gammal granskog med inslag av björk.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131154324</v>
+        <v>131187645</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,37 +1716,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Bod-tjärnen Sydväst, Jmt</t>
+          <t>Nästflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445031</v>
+        <v>445002</v>
       </c>
       <c r="R10" t="n">
-        <v>7053166</v>
+        <v>7053487</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1783,7 +1780,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,54 +1789,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131154314</v>
+        <v>131187647</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,37 +1818,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stor-Bod-tjärnen Sydväst, Jmt</t>
+          <t>Nästflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445069</v>
+        <v>444956</v>
       </c>
       <c r="R11" t="n">
-        <v>7053165</v>
+        <v>7053468</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1914,7 +1882,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1923,54 +1891,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131154316</v>
+        <v>131187648</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,37 +1920,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stor-Bod-tjärnen Sydväst, Jmt</t>
+          <t>Nästflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445069</v>
+        <v>444957</v>
       </c>
       <c r="R12" t="n">
-        <v>7053221</v>
+        <v>7053350</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2045,7 +1984,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2054,81 +1993,60 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131154322</v>
+        <v>131154305</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>57132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2136,10 +2054,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445001</v>
+        <v>444982</v>
       </c>
       <c r="R13" t="n">
-        <v>7053337</v>
+        <v>7053382</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,7 +2094,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växer på en tydligt gammal gran med grov bark.</t>
+          <t>Färsk spillning ovanpå snötäcket och en nyligen använd lega inunder snön.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2185,7 +2103,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2194,24 +2111,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Flerskiktad gammal granskog med inslag av björk.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2229,14 +2131,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131154318</v>
+        <v>131154313</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2267,10 +2169,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444968</v>
+        <v>445053</v>
       </c>
       <c r="R14" t="n">
-        <v>7053470</v>
+        <v>7053130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2303,6 +2205,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2355,14 +2262,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131154321</v>
+        <v>131154314</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2393,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444974</v>
+        <v>445069</v>
       </c>
       <c r="R15" t="n">
-        <v>7053372</v>
+        <v>7053165</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2429,6 +2336,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2481,14 +2393,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131154320</v>
+        <v>131154315</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2519,10 +2431,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444986</v>
+        <v>445094</v>
       </c>
       <c r="R16" t="n">
-        <v>7053440</v>
+        <v>7053203</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2557,11 +2469,6 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Växer på en tydligt gammal gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2587,14 +2494,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2612,41 +2514,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131187652</v>
+        <v>131154316</v>
       </c>
       <c r="B17" t="n">
-        <v>91848</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nästflon, Jmt</t>
+          <t>Stor-Bod-tjärnen Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444993</v>
+        <v>445069</v>
       </c>
       <c r="R17" t="n">
-        <v>7053354</v>
+        <v>7053221</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2681,69 +2590,103 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187648</v>
+        <v>131154317</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nästflon, Jmt</t>
+          <t>Stor-Bod-tjärnen Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444957</v>
+        <v>445064</v>
       </c>
       <c r="R18" t="n">
-        <v>7053350</v>
+        <v>7053303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2780,7 +2723,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2789,63 +2732,92 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131187645</v>
+        <v>131154323</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nästflon, Jmt</t>
+          <t>Stor-Bod-tjärnen Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445002</v>
+        <v>445033</v>
       </c>
       <c r="R19" t="n">
-        <v>7053487</v>
+        <v>7053229</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2880,74 +2852,93 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131187643</v>
+        <v>131154324</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nästflon, Jmt</t>
+          <t>Stor-Bod-tjärnen Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445085</v>
+        <v>445031</v>
       </c>
       <c r="R20" t="n">
-        <v>7053298</v>
+        <v>7053166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2984,7 +2975,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2993,28 +2984,54 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187644</v>
+        <v>131187643</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3046,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445078</v>
+        <v>445085</v>
       </c>
       <c r="R21" t="n">
-        <v>7053300</v>
+        <v>7053298</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3086,7 +3103,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3113,10 +3130,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131187651</v>
+        <v>131187644</v>
       </c>
       <c r="B22" t="n">
-        <v>91848</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,19 +3141,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3144,10 +3165,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445102</v>
+        <v>445078</v>
       </c>
       <c r="R22" t="n">
-        <v>7053266</v>
+        <v>7053300</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3180,6 +3201,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3206,10 +3232,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131187650</v>
+        <v>131187646</v>
       </c>
       <c r="B23" t="n">
-        <v>91848</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3217,19 +3243,23 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3237,10 +3267,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445135</v>
+        <v>445020</v>
       </c>
       <c r="R23" t="n">
-        <v>7053243</v>
+        <v>7053542</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3273,6 +3303,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 979-2026 artfynd.xlsx
+++ b/artfynd/A 979-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154313</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154314</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1055,6 +1070,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154315</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1186,6 +1206,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154316</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,6 +1342,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154317</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1443,6 +1473,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154318</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1574,6 +1609,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154319</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1705,6 +1745,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154320</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1831,6 +1876,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154321</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1962,6 +2012,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154322</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2083,6 +2138,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154323</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2214,6 +2274,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154324</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2349,6 +2414,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154302</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2489,6 +2559,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154303</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2599,6 +2674,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187642</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2701,6 +2781,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187643</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2803,6 +2888,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187644</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2905,6 +2995,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187645</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3007,6 +3102,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187646</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3109,6 +3209,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187647</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3211,6 +3316,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131187648</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3331,8 +3441,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154305</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>